--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.63200144252328</v>
+        <v>7.902700234410033</v>
       </c>
       <c r="D2" t="n">
-        <v>49.51380354879178</v>
+        <v>8.045993076678664</v>
       </c>
       <c r="E2" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F2" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.74183145906355</v>
+        <v>7.595547612097828</v>
       </c>
       <c r="D3" t="n">
-        <v>47.43842214061523</v>
+        <v>7.708743597849975</v>
       </c>
       <c r="E3" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F3" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>57.42887832306378</v>
+        <v>9.332192727497864</v>
       </c>
       <c r="D4" t="n">
-        <v>51.46665483239372</v>
+        <v>8.36333141026398</v>
       </c>
       <c r="E4" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F4" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.55903598327464</v>
+        <v>8.05334334728213</v>
       </c>
       <c r="D5" t="n">
-        <v>49.90840609144613</v>
+        <v>8.110115989859997</v>
       </c>
       <c r="E5" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F5" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>64.64395986900249</v>
+        <v>10.5046434787129</v>
       </c>
       <c r="D6" t="n">
-        <v>65.68119707987822</v>
+        <v>10.67319452548021</v>
       </c>
       <c r="E6" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F6" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.07098508348074</v>
+        <v>8.461535076065621</v>
       </c>
       <c r="D7" t="n">
-        <v>53.09525890704123</v>
+        <v>8.627979572394201</v>
       </c>
       <c r="E7" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F7" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.92588254573124</v>
+        <v>6.487955913681327</v>
       </c>
       <c r="D8" t="n">
-        <v>35.64053222421157</v>
+        <v>5.79158648643438</v>
       </c>
       <c r="E8" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F8" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>27.55031467022701</v>
+        <v>4.476926133911888</v>
       </c>
       <c r="D9" t="n">
-        <v>28.55886544787666</v>
+        <v>4.640815635279957</v>
       </c>
       <c r="E9" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F9" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>42.93974932971443</v>
+        <v>6.977709266078596</v>
       </c>
       <c r="D10" t="n">
-        <v>42.41391710798529</v>
+        <v>6.89226153004761</v>
       </c>
       <c r="E10" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F10" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>48.48193663848094</v>
+        <v>7.878314703753153</v>
       </c>
       <c r="D11" t="n">
-        <v>49.33297714843247</v>
+        <v>8.016608786620276</v>
       </c>
       <c r="E11" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F11" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>24.77928735331643</v>
+        <v>4.026634194913919</v>
       </c>
       <c r="D12" t="n">
-        <v>26.18961336322587</v>
+        <v>4.255812171524204</v>
       </c>
       <c r="E12" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F12" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.25100788500917</v>
+        <v>5.240788781313991</v>
       </c>
       <c r="D13" t="n">
-        <v>35.73945202193524</v>
+        <v>5.807660953564476</v>
       </c>
       <c r="E13" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F13" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>15.39529843602875</v>
+        <v>2.501735995854673</v>
       </c>
       <c r="D14" t="n">
-        <v>14.85209929917109</v>
+        <v>2.413466136115302</v>
       </c>
       <c r="E14" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F14" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>40.09513523146347</v>
+        <v>6.515459475112814</v>
       </c>
       <c r="D15" t="n">
-        <v>32.80617964192309</v>
+        <v>5.331004191812503</v>
       </c>
       <c r="E15" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F15" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>54.95370079364726</v>
+        <v>8.92997637896768</v>
       </c>
       <c r="D16" t="n">
-        <v>54.08851126819992</v>
+        <v>8.789383081082487</v>
       </c>
       <c r="E16" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F16" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>73.18874981814335</v>
+        <v>11.8931718454483</v>
       </c>
       <c r="D17" t="n">
-        <v>72.59029462467909</v>
+        <v>11.79592287651035</v>
       </c>
       <c r="E17" t="n">
-        <v>14.44700183986529</v>
+        <v>2.34763779897811</v>
       </c>
       <c r="F17" t="n">
-        <v>14.36731001651462</v>
+        <v>2.334687877683626</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
